--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/1341-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/1341-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E4E30CB2-9CAB-47A4-BBAD-50ADCF46A70B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4CFE4ADD-A91B-4AFD-95BB-9ECA18D2E608}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{202CEB29-2ACE-4E00-881E-8FD54C46B556}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{191278EF-24E3-40A3-984F-09028109A97C}"/>
   </bookViews>
   <sheets>
     <sheet name="1341-dividend-20260215_1_2" sheetId="1" r:id="rId1"/>
@@ -1472,22 +1472,22 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F0ED251-CC2B-4D18-9E3C-B9B3B123E616}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D042D5BC-E6D0-4B6C-AF42-3C5B9F02F589}">
   <dimension ref="A1:X30"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.375" customWidth="1"/>
-    <col min="2" max="2" width="4.875" customWidth="1"/>
-    <col min="3" max="3" width="11.125" customWidth="1"/>
-    <col min="4" max="6" width="7.125" customWidth="1"/>
-    <col min="7" max="9" width="6.75" customWidth="1"/>
-    <col min="10" max="10" width="7.125" customWidth="1"/>
-    <col min="11" max="22" width="6.75" customWidth="1"/>
-    <col min="23" max="23" width="7.125" customWidth="1"/>
-    <col min="24" max="24" width="9" customWidth="1"/>
+    <col min="1" max="1" width="3.77734375" customWidth="1"/>
+    <col min="2" max="2" width="4.21875" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" customWidth="1"/>
+    <col min="4" max="6" width="6.109375" customWidth="1"/>
+    <col min="7" max="9" width="5.88671875" customWidth="1"/>
+    <col min="10" max="10" width="6.109375" customWidth="1"/>
+    <col min="11" max="22" width="5.88671875" customWidth="1"/>
+    <col min="23" max="23" width="6.109375" customWidth="1"/>
+    <col min="24" max="24" width="6.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
@@ -1521,7 +1521,7 @@
       <c r="W1" s="28"/>
       <c r="X1" s="20"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="21" t="s">
         <v>1</v>
       </c>
@@ -1557,7 +1557,7 @@
       <c r="W2" s="30"/>
       <c r="X2" s="31"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="21" t="s">
         <v>2</v>
       </c>
@@ -1609,7 +1609,7 @@
       </c>
       <c r="X3" s="34"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="23"/>
       <c r="B4" s="24"/>
       <c r="C4" s="7"/>
@@ -1677,7 +1677,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="35">
         <v>2025</v>
       </c>
@@ -1749,7 +1749,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="11" t="s">
         <v>29</v>
       </c>
@@ -1823,7 +1823,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="11" t="s">
         <v>29</v>
       </c>
@@ -1897,7 +1897,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="11" t="s">
         <v>29</v>
       </c>
@@ -1971,7 +1971,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="37">
         <v>2024</v>
       </c>
@@ -2043,7 +2043,7 @@
         <v>9.42</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="16" t="s">
         <v>29</v>
       </c>
@@ -2117,7 +2117,7 @@
         <v>9.42</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="16" t="s">
         <v>29</v>
       </c>
@@ -2191,7 +2191,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="16" t="s">
         <v>29</v>
       </c>
@@ -2265,7 +2265,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="16" t="s">
         <v>29</v>
       </c>
@@ -2339,7 +2339,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="35">
         <v>2023</v>
       </c>
@@ -2411,7 +2411,7 @@
         <v>7.29</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="11" t="s">
         <v>29</v>
       </c>
@@ -2485,7 +2485,7 @@
         <v>7.29</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="11" t="s">
         <v>29</v>
       </c>
@@ -2559,7 +2559,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="11" t="s">
         <v>29</v>
       </c>
@@ -2633,7 +2633,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="11" t="s">
         <v>29</v>
       </c>
@@ -2707,7 +2707,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="11" t="s">
         <v>29</v>
       </c>
@@ -2781,7 +2781,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="11" t="s">
         <v>29</v>
       </c>
@@ -2855,7 +2855,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="37">
         <v>2022</v>
       </c>
@@ -2927,7 +2927,7 @@
         <v>9.65</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="16" t="s">
         <v>29</v>
       </c>
@@ -3001,7 +3001,7 @@
         <v>4.78</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="16" t="s">
         <v>29</v>
       </c>
@@ -3075,7 +3075,7 @@
         <v>4.87</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="16" t="s">
         <v>29</v>
       </c>
@@ -3149,7 +3149,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="35">
         <v>2021</v>
       </c>
@@ -3221,7 +3221,7 @@
         <v>9.33</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="37">
         <v>2020</v>
       </c>
@@ -3293,7 +3293,7 @@
         <v>10.3</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="35">
         <v>2019</v>
       </c>
@@ -3365,7 +3365,7 @@
         <v>9.36</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="37">
         <v>2018</v>
       </c>
@@ -3437,7 +3437,7 @@
         <v>6.54</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="35">
         <v>2017</v>
       </c>
@@ -3509,7 +3509,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="37" t="s">
         <v>45</v>
       </c>
